--- a/data/a8-import/アフィリエイト案件_転職エージェント図鑑.xlsx
+++ b/data/a8-import/アフィリエイト案件_転職エージェント図鑑.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="146">
   <si>
     <t>反映</t>
   </si>
@@ -12561,6 +12561,241 @@
       <t>。</t>
     </r>
   </si>
+  <si>
+    <t>Ａｖａｌｏｎ＿Ｃｏｎｓｕｌｔｉｎｇ株式会社</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC2EM+27S3UA+5GTK+TRVYQ" rel="nofollow"&gt;20代のキャリアを本気で変える、転職成功保証付き専門塾【ホワイトアカデミー「20代キャリア形成・転職サポートコース」】&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www17.a8.net/0.gif?a8mat=4BC2EM+27S3UA+5GTK+TRVYQ" alt=""&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">◆セールスポイント◆
+・転職成功保証があり、カリキュラムを消化したものの、ホワイト企業総合研究所がホワイト企業と定めた会社に１社も内定できなければ授業料を返金します。
+・自己分析からキャリア計画・企業選定・選考対策・入社後定着まで、一貫した包括的サポートを提供します。
+・70名以上の業界経験者講師が在籍し、面接練習回数無制限＋24時間チャットサポートで徹底支援します。
+・5年後・10年後の理想像から逆算した長期キャリア設計で、「理想のキャリア実現」を最終ゴールに据えます。
+◆ターゲットユーザー◆
+・21〜29歳で、ブラック企業脱出・低年収改善・キャリアの軸づくりに悩んでいる方。
+・新卒での就職に失敗した方や、キャリアの方向性が見つからず迷子になっている第二新卒・既卒の方。
+・従来の無料転職エージェントでは解決できなかった根本的なキャリア課題を抱えている方。
+◆おススメの提案の仕方◆
+・「ブラック企業脱出」「20代キャリア」「転職成功保証」などのテーマで
+　悩み解決型の記事から無料相談へ誘導する方法が効果的です。
+・無料エージェントとの違いや、転職成功保証・返金制度を軸にしたサービス比較記事での紹介がおすすめです。
+・早期入塾による生涯年収の差を訴求したコンテンツは、20代読者への刺さりが強く成果に繋がりやすいです。
+</t>
+  </si>
+  <si>
+    <t>ポジウィル株式会社</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC2EM+1PX3OY+5H76+HV7V6" rel="nofollow"&gt;信頼できる1人に出会える！納得転職のエージェント紹介【POSIWILLエージェント紹介】&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www15.a8.net/0.gif?a8mat=4BC2EM+1PX3OY+5H76+HV7V6" alt=""&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">◆セールスポイント◆
+・独自審査を通過した信頼できるエージェントのみを厳選し、最適な1〜2名に絞って紹介するため「比較疲れ」が起きません。
+・内定数より「納得度」を重視した意思決定支援で、転職後のミスマッチを防ぎます。
+・初回60分の無料キャリア相談で志向性を整理するため、転職の方向性が曖昧な方でも安心してスタートできます。
+・全国オンライン対応で、どこからでも気軽にキャリア相談が可能です。
+◆ターゲットユーザー◆
+・転職に不安や悩みを持ち、信頼できるエージェントをどう選べばよいか分からない20〜30代の方。
+・多数のエージェントに同時登録して比較することに疲れを感じ、本質的なサポートを求めている方。
+・ハイキャリア・エンジニア・営業・経理など多様な職種で転職を検討しているが、焦らず自分に合った選択をしたい方。
+◆おススメの提案の仕方◆
+・「転職エージェント 選び方」「転職エージェント 比較」など、エージェント選びに迷う層に刺さるキーワードの記事でご紹介いただくと効果的です。
+・「比較疲れ・エージェント選びに失敗した経験がある方へ」という共感型の訴求で、再出発を後押しする切り口がおすすめです。
+・無理な転職勧誘なし・完全無料という安心感と、
+　50,000人以上の支援実績・顧客満足度92%という実績をセットでお伝えいただくと信頼感が高まります。
+</t>
+  </si>
+  <si>
+    <t>ＭｙＶｉｓｉｏｎ/コンサル特化</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC2EM+1I6GTU+5B0Y+62U36" rel="nofollow"&gt;【MyVision（人事特化）】&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www17.a8.net/0.gif?a8mat=4BC2EM+1I6GTU+5B0Y+62U36" alt=""&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">◆メインターゲット◆
+1. コンサル業界未経験の方
+MyVision利用者の9割はコンサル業界未経験の方です。
+2. 20代後半から30代前半の方
+MyVision利用者の9割の方は20代後半から30代前半の方です。
+3. 大手企業・IT系の企業・官公庁などのバックグラウンドをお持ちの方
+MyVision利用者多くの方が大手企業ご出身の方です。
+大手でなくても、以下のご経験をお持ちの方が多いです。
+1. エンジニア
+2. プロジェクトマネジメント経験がある方
+3. 企画経験（営業企画・経営企画・総務企画・人事企画など）
+4. 会計や財務など、高い専門性がある方
+詳細については、以下をご確認くださいませ。
+https://docs.google.com/presentation/d/115LgJGDPw6Fu3W0Y-L6fghinomsTnQ0JF1gTZhNGJyE/edit?usp=sharing
+◆セールスポイント◆
+MyVisionはアクセンチュアやBIG4といった外資系コンサルティングファームや
+ベイカレントコンサルティングといった国内の人気ファームへの転職支援が強いコンサル業界特化の転職エージェントです。
+20代〜30代のハイクラス層の方を中心に、コンサル業界へ転職を支援しています。
+◆おススメの提案の仕方◆
+＜実績と独自求人＞
+クライアントポートフォリオが豊富であり、非公開求人数多くご用意できるのが弊社の強みになります。
+また、求職者様の経験に合わせてベストな求人を提案いたします。
+＜選考対策のクオリティ＞
+大手エージェントでは実施していない、模擬面接やケース面接対策、履歴書の添削を全て無料で提供しております。
+元コンサルタントを相手に何度も練習することが可能です。
+このため、求職者様は本番前に準備をした上で、面接に参加することが可能です。
+</t>
+  </si>
+  <si>
+    <t>イノセル株式会社</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC2EM+1SW9PU+5QK4+5YJRM" rel="nofollow"&gt;20代の営業職への転職なら【イノセル】&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www13.a8.net/0.gif?a8mat=4BC2EM+1SW9PU+5QK4+5YJRM" alt=""&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イノセルは「営業を面白くする」をミッションに掲げる、
+営業職に完全特化した転職エージェントサービスです。
+◆セールスポイント（サービスの集客に強調できる特長）◆
+○内定率69.1%・書類通過率88.2%：
+業界トップクラスの決定率を誇り、市場価値を最大限に高めるサポート
+○定着率97.7%：
+入社後の活躍と定着を重視。単なる内定獲得ではなく「強みを発揮し、長く活躍できる企業」とのマッチング
+○営業職に特化したプロの知見：
+担当コンサルタントは営業経験者が多く、営業経験・スキルを深く理解。
+他エージェントでは見過ごされがちな潜在的な強みや、企業が求める「どんな人物か」までを的確に見極め、
+ミスマッチのない提案が可能
+○市場価値をあげるキャリア戦略の構築：
+将来の志向性や価値観、培ってきた能力を深く掘り下げ、
+「なりたい姿」に近づくための戦略を一緒に作り上げます。
+▼ターゲットユーザー：
+特に強みとするターゲット層は「20代の営業職経験者」です。
+○性別・年齢層：
+男女問わず、20代が中心。特に、キャリアの方向性に悩む20代の若手営業職
+○職業・経験： 法人営業、個人営業、販売職など、何らかの営業経験がある方。
+○志向性：
+「もっと営業として成長したい」「市場価値を高めたい」という上昇志向が強い方。
+「今の会社では営業の面白さが感じられない」「正当な評価や報酬を得たい」と感じている方。
+大手エージェントで一般的な求人紹介しか受けられず「専門的なキャリアアドバイス」を求めている方。</t>
+  </si>
+  <si>
+    <t>株式会社エムエム総研</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC2EM+1MCI2A+4SMG+60WN6" rel="nofollow"&gt;マーキャリNEXT CAREERの無料キャリア面談に申し込む&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www17.a8.net/0.gif?a8mat=4BC2EM+1MCI2A+4SMG+60WN6" alt=""&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「マーキャリNEXT CAREER」はSaaS業界に特化した転職エージェントサービスです。
+媒体資料はこちら
+◆特長◆
+SaaS特化だからこそ【企業との関係性、情報深度に強み】
+・SaaS業界全体、また企業単位の事業成長率など最新動向を有し企業選びをご支援
+・採用枠を弊社で充足するなど企業様から高くご評価をいただいています
+SaaS特化だからこそ【圧倒的な選考対策の充実】
+・過去面接で聞かれた質問リストなど個社単位で選考対策が充実
+・書類選考通過率94％、内定率20%（※2024年度実績）
+「ご自身のキャリアは納得して決めてほしい」
+そのために必要な【情報提供】と【選考対策】を充実させ、
+特化型エージェントとして提供できる最大限のサービス品質で
+満足してご利用いただけるように日々努めております。
+その他、担当CAとはLINEを通じて、気軽に連絡が取れるようになっています。
+◆ご利用者の声◆　※利用者満足度97%（2025年6月時点 自社アンケートより）
+・「寄り添った支援、実績、ノウハウ、お人柄などこれ以上にないバックアップでした」
+・「選考書類の添削が比にならないほどよかった。通過率が劇的に変わりました」
+ご利用者の声ページ
+◆受賞歴・評価◆　※媒体資料に記載
+『みんなのキャリアAWARD』2年連続2部門最優秀賞W受賞
+SaaS人事担当者の86％が【注目する】と回答
+◆ブランディング動画◆
+マーキャリのCAたちが、
+「どのような想いで転職希望者の方々と向き合っているのか」
+私たち自身の言葉でお伝えすることで、
+安心してキャリア選択を進めるきっかけになればと思っています。
+詳細はこちら
+◆ターゲット◆
+・20代、30代、転職を検討している営業経験者　※業界未経験OK
+※SaaS企業各社国内都心部に構えているため勤務可能な方が対象</t>
+  </si>
+  <si>
+    <t>株式会社メディカルリソース</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC2EM+QSJ02+276A+5ZEMQ" rel="nofollow"&gt;自由テキスト&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www10.a8.net/0.gif?a8mat=4BC2EM+QSJ02+276A+5ZEMQ" alt=""&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">▼ファルマスタッフの特徴
+◎求人票にはない「職場のリアルな実態」も事前にお伝え
+◎人員構成や機材など、直接訪問で得たリアルな情報をご提供
+◎地域密着！その地域の内情に詳しいエリア担当コンサルタントがサポート
+◎経験豊富なコンサルタントが多く「条件交渉力」に自信あり
+◎直接訪問で築いた「医療機関との良好な関係」があるからこそ引き出せるリアルな情報
+◎20代〜50代まで対応！調剤薬局・病院・企業など幅広い選択肢
+◎過去データに基づく面接対策と、状況に応じた面接同席で、入社後のギャップを軽減
+【情報力とミスマッチ軽減をアピール】
+ご紹介先はできる限りコンサルタントが直接訪問し、人員構成や利用機材まで詳しく確認。
+求人票だけでは見えない「職場のリアルな実態」を事前にお伝えすることで、入社後のミスマッチの軽減を目指します
+【コンサルタントの交渉力と地域密着をアピール】
+その地域の内情に詳しいエリア担当コンサルタントが求職者様をしっかりとサポート。
+医療機関と良好な関係性を築いている経験豊富なコンサルタントが多数在籍しており、「高い条件交渉力」に定評あり
+【手厚い選考サポートと安心感をアピール】
+過去のデータに基づいた面接・書類対策はもちろん、ご希望や企業の状況に応じ、面接同席も実施。
+双方の確認不足を防ぐようサポートし、長期的に安心して働ける職場探しをお手伝い
+【幅広い選択肢とキャリアチェンジ支援をアピール】
+調剤薬局や病院、企業など幅広い求人を扱っており、20代〜50代まで世代を問わずサポート可能。
+異業種への新たなチャレンジを目指す方にもこれまでの経験を活かしたあなたに合ったキャリアをご提案
+【医療機関との信頼関係をアピール】
+コンサルタントの異動が少なく直接訪問を重ねることで医療機関と良好な関係性を築いています。
+現場の担当者とコミュニケーションをとっているからこそ、求人票以上のリアルな情報提供やスムーズな条件交渉が可能</t>
+  </si>
+  <si>
+    <t>株式会社ウズウズ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第二新卒・既卒・フリーター向け就職・転職サポート&lt;BR&gt;
+&lt;A href="https://px.a8.net/svt/ejp?a8mat=4BC2EM+2Z6SY+33T0+5YJRM" rel="nofollow"&gt;まずは無料相談&lt;B&gt;【UZUZ第二新卒】&lt;/B&gt;&lt;/A&gt;
+&lt;img border="0" width="1" height="1" src="https://www12.a8.net/0.gif?a8mat=4BC2EM+2Z6SY+33T0+5YJRM" alt=""&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">◆UZUZ第二新卒とは
+20代の第二新卒の転職サポートを完全無料で提供しています。
+◆ターゲット
+年齢：29歳まで
+属性：第二新卒がメインとなります。
+※既卒、就職浪人、大学中退、フリーター、ニートなど転職希望者も対象ですが、このような属性に訴求する場合は
+既卒・フリーター向け就職エージェント【UZUZ既卒】(15-0311)のプログラムをご参照ください。
+◆セールスポイント
+1 信頼のおける実績
+・就職支援実績　68,374名(2024/12/12時点)
+・入社後の定着率 93.6%
+・大手からベンチャーまで 登録企業者数 3,000社以上
+2 安心のサポート体制
+・日本で唯一キャリアカウンセラーの9割が元既卒・第二新卒
+・エントリーや入社を強要するような行為は行っておりません
+・職務経歴書や自己PR文の添削、模擬面接など、一人ひとりに合わせた対策を丁寧に行います
+3 ブラック企業を徹底排除
+・離職率/労働時間/社会保険の有無/雇用形態などで厳しい基準を設定
+・厳格なスクリーニング体制：新規契約時に入念な事前リサーチを行い、
+　ブラック企業の疑いがある会社との提携を未然に防ぐ体制を構築。
+・入社後の継続的なヒアリング：入社1ヶ月、3ヶ月、6ヶ月のタイミングで定期面談を実施
+◆「スピード」より「丁寧さ」を重視
+単なる「最短内定」ではなく、丁寧なヒアリングを通じて個々の悩みや将来に寄り添うことで失敗しないキャリア支援を心がけています。
+◆利用者(一例)
+・転職3回、キャリアが崩れてしまい就活難航(28歳)
+・新卒で入った会社を1ヶ月で退職(23歳)
+・激務で疲弊し休職。復帰したもののすぐに退職(25歳)
+◆就職実績
+・不動産営業 短期離職→大手人材会社 人材紹介営業
+年収350万円→450万円(24歳)
+・保育士 転職3回→メーカー企業の営業事務
+年収220万円→400万円(28歳)
+公務員→IT業界システムエンジニア
+年収400円→480万円(29歳)
+【登録者数 8万人超えのYouTube「ひろさんチャンネル」ご紹介】
+就職・転職活動へ役立つノウハウを日々配信中です。
+▼メディア会員の方への動画はこちら
+https://tinyurl.com/ycxs537z</t>
+  </si>
 </sst>
 </file>
 
@@ -13923,9 +14158,15 @@
       <c r="A26" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>127</v>
+      </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -13954,9 +14195,15 @@
       <c r="A27" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -13985,9 +14232,15 @@
       <c r="A28" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>133</v>
+      </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -14016,9 +14269,15 @@
       <c r="A29" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -14047,9 +14306,15 @@
       <c r="A30" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -14078,9 +14343,15 @@
       <c r="A31" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="2"/>
+      <c r="B31" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -14109,9 +14380,15 @@
       <c r="A32" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="2"/>
+      <c r="B32" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>

--- a/data/a8-import/アフィリエイト案件_転職エージェント図鑑.xlsx
+++ b/data/a8-import/アフィリエイト案件_転職エージェント図鑑.xlsx
@@ -14156,7 +14156,7 @@
     </row>
     <row r="26" ht="27.75" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>125</v>
@@ -14193,7 +14193,7 @@
     </row>
     <row r="27" ht="27.75" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>128</v>
@@ -14230,7 +14230,7 @@
     </row>
     <row r="28" ht="27.75" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>131</v>
@@ -14267,7 +14267,7 @@
     </row>
     <row r="29" ht="27.75" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>134</v>
@@ -14304,7 +14304,7 @@
     </row>
     <row r="30" ht="27.75" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>137</v>
@@ -14341,7 +14341,7 @@
     </row>
     <row r="31" ht="27.75" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>140</v>
@@ -14378,7 +14378,7 @@
     </row>
     <row r="32" ht="27.75" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>143</v>
